--- a/raw/Timetable_2026Autumn_2026SE.xlsx
+++ b/raw/Timetable_2026Autumn_2026SE.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30425"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="35" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D66567C-1B6B-4646-92E6-77475516F695}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{414F6552-216E-4507-BCB8-3BF6D1640423}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="188">
   <si>
     <t>week</t>
   </si>
@@ -362,9 +362,6 @@
   </si>
   <si>
     <t>30       Oct.</t>
-  </si>
-  <si>
-    <t>B307</t>
   </si>
   <si>
     <t>31       Oct.</t>
@@ -1032,6 +1029,51 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1068,24 +1110,6 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1102,33 +1126,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1479,81 +1476,81 @@
   <sheetData>
     <row r="1" spans="1:28" ht="13.9" customHeight="1"/>
     <row r="2" spans="1:28" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="33" t="s">
+      <c r="C2" s="63"/>
+      <c r="D2" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="34"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="33" t="s">
+      <c r="E2" s="49"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="34"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="33" t="s">
+      <c r="H2" s="49"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="34"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="33" t="s">
+      <c r="K2" s="49"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="34"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="33" t="s">
+      <c r="N2" s="49"/>
+      <c r="O2" s="50"/>
+      <c r="P2" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="33" t="s">
+      <c r="Q2" s="49"/>
+      <c r="R2" s="50"/>
+      <c r="S2" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="34"/>
-      <c r="U2" s="35"/>
+      <c r="T2" s="49"/>
+      <c r="U2" s="50"/>
     </row>
     <row r="3" spans="1:28" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="52"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="33" t="s">
+      <c r="A3" s="61"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="34"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="33" t="s">
+      <c r="E3" s="49"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="34"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="33" t="s">
+      <c r="H3" s="49"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="34"/>
-      <c r="L3" s="35"/>
-      <c r="M3" s="33" t="s">
+      <c r="K3" s="49"/>
+      <c r="L3" s="50"/>
+      <c r="M3" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="34"/>
-      <c r="O3" s="35"/>
-      <c r="P3" s="33" t="s">
+      <c r="N3" s="49"/>
+      <c r="O3" s="50"/>
+      <c r="P3" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="34"/>
-      <c r="R3" s="35"/>
-      <c r="S3" s="33" t="s">
+      <c r="Q3" s="49"/>
+      <c r="R3" s="50"/>
+      <c r="S3" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="34"/>
-      <c r="U3" s="35"/>
+      <c r="T3" s="49"/>
+      <c r="U3" s="50"/>
     </row>
     <row r="4" spans="1:28" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="45">
+      <c r="A4" s="42">
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -1590,7 +1587,7 @@
       </c>
     </row>
     <row r="5" spans="1:28" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="46"/>
+      <c r="A5" s="43"/>
       <c r="B5" s="6" t="s">
         <v>21</v>
       </c>
@@ -1650,7 +1647,7 @@
       </c>
     </row>
     <row r="6" spans="1:28" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="46"/>
+      <c r="A6" s="43"/>
       <c r="B6" s="6" t="s">
         <v>28</v>
       </c>
@@ -1710,7 +1707,7 @@
       </c>
     </row>
     <row r="7" spans="1:28" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="46"/>
+      <c r="A7" s="43"/>
       <c r="B7" s="6" t="s">
         <v>32</v>
       </c>
@@ -1768,7 +1765,7 @@
       </c>
     </row>
     <row r="8" spans="1:28" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="46"/>
+      <c r="A8" s="43"/>
       <c r="B8" s="6" t="s">
         <v>36</v>
       </c>
@@ -1827,7 +1824,7 @@
       <c r="AB8" s="2"/>
     </row>
     <row r="9" spans="1:28" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="46"/>
+      <c r="A9" s="43"/>
       <c r="B9" s="6" t="s">
         <v>42</v>
       </c>
@@ -1878,7 +1875,7 @@
       <c r="AB9" s="2"/>
     </row>
     <row r="10" spans="1:28" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="47"/>
+      <c r="A10" s="44"/>
       <c r="B10" s="6" t="s">
         <v>46</v>
       </c>
@@ -1922,7 +1919,7 @@
       </c>
     </row>
     <row r="11" spans="1:28" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="48">
+      <c r="A11" s="45">
         <v>2</v>
       </c>
       <c r="B11" s="14" t="s">
@@ -1972,7 +1969,7 @@
       </c>
     </row>
     <row r="12" spans="1:28" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="49"/>
+      <c r="A12" s="46"/>
       <c r="B12" s="14" t="s">
         <v>51</v>
       </c>
@@ -2030,7 +2027,7 @@
       </c>
     </row>
     <row r="13" spans="1:28" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="49"/>
+      <c r="A13" s="46"/>
       <c r="B13" s="14" t="s">
         <v>52</v>
       </c>
@@ -2100,7 +2097,7 @@
       </c>
     </row>
     <row r="14" spans="1:28" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="49"/>
+      <c r="A14" s="46"/>
       <c r="B14" s="14" t="s">
         <v>56</v>
       </c>
@@ -2143,7 +2140,7 @@
       <c r="U14" s="17"/>
     </row>
     <row r="15" spans="1:28" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="49"/>
+      <c r="A15" s="46"/>
       <c r="B15" s="14" t="s">
         <v>57</v>
       </c>
@@ -2184,7 +2181,7 @@
       <c r="U15" s="17"/>
     </row>
     <row r="16" spans="1:28" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="49"/>
+      <c r="A16" s="46"/>
       <c r="B16" s="14" t="s">
         <v>58</v>
       </c>
@@ -2219,7 +2216,7 @@
       <c r="U16" s="17"/>
     </row>
     <row r="17" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="50"/>
+      <c r="A17" s="47"/>
       <c r="B17" s="14" t="s">
         <v>59</v>
       </c>
@@ -2246,7 +2243,7 @@
       <c r="U17" s="17"/>
     </row>
     <row r="18" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="45">
+      <c r="A18" s="42">
         <v>3</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -2274,7 +2271,7 @@
       <c r="U18" s="9"/>
     </row>
     <row r="19" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="46"/>
+      <c r="A19" s="43"/>
       <c r="B19" s="6" t="s">
         <v>61</v>
       </c>
@@ -2317,7 +2314,7 @@
       <c r="U19" s="9"/>
     </row>
     <row r="20" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="46"/>
+      <c r="A20" s="43"/>
       <c r="B20" s="6" t="s">
         <v>62</v>
       </c>
@@ -2372,7 +2369,7 @@
       </c>
     </row>
     <row r="21" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="46"/>
+      <c r="A21" s="43"/>
       <c r="B21" s="6" t="s">
         <v>63</v>
       </c>
@@ -2415,7 +2412,7 @@
       <c r="U21" s="9"/>
     </row>
     <row r="22" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="46"/>
+      <c r="A22" s="43"/>
       <c r="B22" s="6" t="s">
         <v>64</v>
       </c>
@@ -2456,7 +2453,7 @@
       <c r="U22" s="9"/>
     </row>
     <row r="23" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="46"/>
+      <c r="A23" s="43"/>
       <c r="B23" s="6" t="s">
         <v>65</v>
       </c>
@@ -2483,7 +2480,7 @@
       <c r="U23" s="9"/>
     </row>
     <row r="24" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="47"/>
+      <c r="A24" s="44"/>
       <c r="B24" s="22" t="s">
         <v>66</v>
       </c>
@@ -2510,7 +2507,7 @@
       <c r="U24" s="25"/>
     </row>
     <row r="25" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="48">
+      <c r="A25" s="45">
         <v>4</v>
       </c>
       <c r="B25" s="14" t="s">
@@ -2555,7 +2552,7 @@
       <c r="U25" s="17"/>
     </row>
     <row r="26" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="49"/>
+      <c r="A26" s="46"/>
       <c r="B26" s="14" t="s">
         <v>68</v>
       </c>
@@ -2598,7 +2595,7 @@
       <c r="U26" s="17"/>
     </row>
     <row r="27" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="49"/>
+      <c r="A27" s="46"/>
       <c r="B27" s="14" t="s">
         <v>69</v>
       </c>
@@ -2653,7 +2650,7 @@
       </c>
     </row>
     <row r="28" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="49"/>
+      <c r="A28" s="46"/>
       <c r="B28" s="14" t="s">
         <v>70</v>
       </c>
@@ -2696,90 +2693,90 @@
       <c r="U28" s="17"/>
     </row>
     <row r="29" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="49"/>
+      <c r="A29" s="46"/>
       <c r="B29" s="26" t="s">
         <v>71</v>
       </c>
       <c r="C29" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="D29" s="36" t="s">
+      <c r="D29" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="E29" s="37"/>
-      <c r="F29" s="37"/>
-      <c r="G29" s="37"/>
-      <c r="H29" s="37"/>
-      <c r="I29" s="37"/>
-      <c r="J29" s="37"/>
-      <c r="K29" s="37"/>
-      <c r="L29" s="37"/>
-      <c r="M29" s="37"/>
-      <c r="N29" s="37"/>
-      <c r="O29" s="37"/>
-      <c r="P29" s="37"/>
-      <c r="Q29" s="37"/>
-      <c r="R29" s="37"/>
-      <c r="S29" s="37"/>
-      <c r="T29" s="37"/>
-      <c r="U29" s="38"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="52"/>
+      <c r="G29" s="52"/>
+      <c r="H29" s="52"/>
+      <c r="I29" s="52"/>
+      <c r="J29" s="52"/>
+      <c r="K29" s="52"/>
+      <c r="L29" s="52"/>
+      <c r="M29" s="52"/>
+      <c r="N29" s="52"/>
+      <c r="O29" s="52"/>
+      <c r="P29" s="52"/>
+      <c r="Q29" s="52"/>
+      <c r="R29" s="52"/>
+      <c r="S29" s="52"/>
+      <c r="T29" s="52"/>
+      <c r="U29" s="53"/>
     </row>
     <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="49"/>
+      <c r="A30" s="46"/>
       <c r="B30" s="26" t="s">
         <v>73</v>
       </c>
       <c r="C30" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="D30" s="39"/>
-      <c r="E30" s="40"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="40"/>
-      <c r="H30" s="40"/>
-      <c r="I30" s="40"/>
-      <c r="J30" s="40"/>
-      <c r="K30" s="40"/>
-      <c r="L30" s="40"/>
-      <c r="M30" s="40"/>
-      <c r="N30" s="40"/>
-      <c r="O30" s="40"/>
-      <c r="P30" s="40"/>
-      <c r="Q30" s="40"/>
-      <c r="R30" s="40"/>
-      <c r="S30" s="40"/>
-      <c r="T30" s="40"/>
-      <c r="U30" s="41"/>
+      <c r="D30" s="54"/>
+      <c r="E30" s="55"/>
+      <c r="F30" s="55"/>
+      <c r="G30" s="55"/>
+      <c r="H30" s="55"/>
+      <c r="I30" s="55"/>
+      <c r="J30" s="55"/>
+      <c r="K30" s="55"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="55"/>
+      <c r="N30" s="55"/>
+      <c r="O30" s="55"/>
+      <c r="P30" s="55"/>
+      <c r="Q30" s="55"/>
+      <c r="R30" s="55"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="55"/>
+      <c r="U30" s="56"/>
     </row>
     <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="50"/>
+      <c r="A31" s="47"/>
       <c r="B31" s="26" t="s">
         <v>74</v>
       </c>
       <c r="C31" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="D31" s="42"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="43"/>
-      <c r="H31" s="43"/>
-      <c r="I31" s="43"/>
-      <c r="J31" s="43"/>
-      <c r="K31" s="43"/>
-      <c r="L31" s="43"/>
-      <c r="M31" s="43"/>
-      <c r="N31" s="43"/>
-      <c r="O31" s="43"/>
-      <c r="P31" s="43"/>
-      <c r="Q31" s="43"/>
-      <c r="R31" s="43"/>
-      <c r="S31" s="43"/>
-      <c r="T31" s="43"/>
-      <c r="U31" s="44"/>
+      <c r="D31" s="57"/>
+      <c r="E31" s="58"/>
+      <c r="F31" s="58"/>
+      <c r="G31" s="58"/>
+      <c r="H31" s="58"/>
+      <c r="I31" s="58"/>
+      <c r="J31" s="58"/>
+      <c r="K31" s="58"/>
+      <c r="L31" s="58"/>
+      <c r="M31" s="58"/>
+      <c r="N31" s="58"/>
+      <c r="O31" s="58"/>
+      <c r="P31" s="58"/>
+      <c r="Q31" s="58"/>
+      <c r="R31" s="58"/>
+      <c r="S31" s="58"/>
+      <c r="T31" s="58"/>
+      <c r="U31" s="59"/>
     </row>
     <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="45">
+      <c r="A32" s="42">
         <v>5</v>
       </c>
       <c r="B32" s="6" t="s">
@@ -2812,7 +2809,7 @@
       <c r="U32" s="9"/>
     </row>
     <row r="33" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="46"/>
+      <c r="A33" s="43"/>
       <c r="B33" s="6" t="s">
         <v>76</v>
       </c>
@@ -2855,7 +2852,7 @@
       <c r="U33" s="9"/>
     </row>
     <row r="34" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="46"/>
+      <c r="A34" s="43"/>
       <c r="B34" s="6" t="s">
         <v>77</v>
       </c>
@@ -2896,117 +2893,117 @@
       <c r="U34" s="9"/>
     </row>
     <row r="35" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="46"/>
+      <c r="A35" s="43"/>
       <c r="B35" s="28" t="s">
         <v>78</v>
       </c>
       <c r="C35" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="D35" s="36" t="s">
+      <c r="D35" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="E35" s="37"/>
-      <c r="F35" s="37"/>
-      <c r="G35" s="37"/>
-      <c r="H35" s="37"/>
-      <c r="I35" s="37"/>
-      <c r="J35" s="37"/>
-      <c r="K35" s="37"/>
-      <c r="L35" s="37"/>
-      <c r="M35" s="37"/>
-      <c r="N35" s="37"/>
-      <c r="O35" s="37"/>
-      <c r="P35" s="37"/>
-      <c r="Q35" s="37"/>
-      <c r="R35" s="37"/>
-      <c r="S35" s="37"/>
-      <c r="T35" s="37"/>
-      <c r="U35" s="38"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="52"/>
+      <c r="I35" s="52"/>
+      <c r="J35" s="52"/>
+      <c r="K35" s="52"/>
+      <c r="L35" s="52"/>
+      <c r="M35" s="52"/>
+      <c r="N35" s="52"/>
+      <c r="O35" s="52"/>
+      <c r="P35" s="52"/>
+      <c r="Q35" s="52"/>
+      <c r="R35" s="52"/>
+      <c r="S35" s="52"/>
+      <c r="T35" s="52"/>
+      <c r="U35" s="53"/>
     </row>
     <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="46"/>
+      <c r="A36" s="43"/>
       <c r="B36" s="28" t="s">
         <v>79</v>
       </c>
       <c r="C36" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="D36" s="39"/>
-      <c r="E36" s="40"/>
-      <c r="F36" s="40"/>
-      <c r="G36" s="40"/>
-      <c r="H36" s="40"/>
-      <c r="I36" s="40"/>
-      <c r="J36" s="40"/>
-      <c r="K36" s="40"/>
-      <c r="L36" s="40"/>
-      <c r="M36" s="40"/>
-      <c r="N36" s="40"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="40"/>
-      <c r="Q36" s="40"/>
-      <c r="R36" s="40"/>
-      <c r="S36" s="40"/>
-      <c r="T36" s="40"/>
-      <c r="U36" s="41"/>
+      <c r="D36" s="54"/>
+      <c r="E36" s="55"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="55"/>
+      <c r="J36" s="55"/>
+      <c r="K36" s="55"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="55"/>
+      <c r="N36" s="55"/>
+      <c r="O36" s="55"/>
+      <c r="P36" s="55"/>
+      <c r="Q36" s="55"/>
+      <c r="R36" s="55"/>
+      <c r="S36" s="55"/>
+      <c r="T36" s="55"/>
+      <c r="U36" s="56"/>
     </row>
     <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="46"/>
+      <c r="A37" s="43"/>
       <c r="B37" s="28" t="s">
         <v>80</v>
       </c>
       <c r="C37" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="D37" s="39"/>
-      <c r="E37" s="40"/>
-      <c r="F37" s="40"/>
-      <c r="G37" s="40"/>
-      <c r="H37" s="40"/>
-      <c r="I37" s="40"/>
-      <c r="J37" s="40"/>
-      <c r="K37" s="40"/>
-      <c r="L37" s="40"/>
-      <c r="M37" s="40"/>
-      <c r="N37" s="40"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="40"/>
-      <c r="Q37" s="40"/>
-      <c r="R37" s="40"/>
-      <c r="S37" s="40"/>
-      <c r="T37" s="40"/>
-      <c r="U37" s="41"/>
+      <c r="D37" s="54"/>
+      <c r="E37" s="55"/>
+      <c r="F37" s="55"/>
+      <c r="G37" s="55"/>
+      <c r="H37" s="55"/>
+      <c r="I37" s="55"/>
+      <c r="J37" s="55"/>
+      <c r="K37" s="55"/>
+      <c r="L37" s="55"/>
+      <c r="M37" s="55"/>
+      <c r="N37" s="55"/>
+      <c r="O37" s="55"/>
+      <c r="P37" s="55"/>
+      <c r="Q37" s="55"/>
+      <c r="R37" s="55"/>
+      <c r="S37" s="55"/>
+      <c r="T37" s="55"/>
+      <c r="U37" s="56"/>
     </row>
     <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="47"/>
+      <c r="A38" s="44"/>
       <c r="B38" s="28" t="s">
         <v>81</v>
       </c>
       <c r="C38" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="D38" s="39"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="40"/>
-      <c r="G38" s="40"/>
-      <c r="H38" s="40"/>
-      <c r="I38" s="40"/>
-      <c r="J38" s="40"/>
-      <c r="K38" s="40"/>
-      <c r="L38" s="40"/>
-      <c r="M38" s="40"/>
-      <c r="N38" s="40"/>
-      <c r="O38" s="40"/>
-      <c r="P38" s="40"/>
-      <c r="Q38" s="40"/>
-      <c r="R38" s="40"/>
-      <c r="S38" s="40"/>
-      <c r="T38" s="40"/>
-      <c r="U38" s="41"/>
+      <c r="D38" s="54"/>
+      <c r="E38" s="55"/>
+      <c r="F38" s="55"/>
+      <c r="G38" s="55"/>
+      <c r="H38" s="55"/>
+      <c r="I38" s="55"/>
+      <c r="J38" s="55"/>
+      <c r="K38" s="55"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="55"/>
+      <c r="N38" s="55"/>
+      <c r="O38" s="55"/>
+      <c r="P38" s="55"/>
+      <c r="Q38" s="55"/>
+      <c r="R38" s="55"/>
+      <c r="S38" s="55"/>
+      <c r="T38" s="55"/>
+      <c r="U38" s="56"/>
     </row>
     <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="48">
+      <c r="A39" s="45">
         <v>6</v>
       </c>
       <c r="B39" s="28" t="s">
@@ -3015,81 +3012,81 @@
       <c r="C39" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="39"/>
-      <c r="E39" s="40"/>
-      <c r="F39" s="40"/>
-      <c r="G39" s="40"/>
-      <c r="H39" s="40"/>
-      <c r="I39" s="40"/>
-      <c r="J39" s="40"/>
-      <c r="K39" s="40"/>
-      <c r="L39" s="40"/>
-      <c r="M39" s="40"/>
-      <c r="N39" s="40"/>
-      <c r="O39" s="40"/>
-      <c r="P39" s="40"/>
-      <c r="Q39" s="40"/>
-      <c r="R39" s="40"/>
-      <c r="S39" s="40"/>
-      <c r="T39" s="40"/>
-      <c r="U39" s="41"/>
+      <c r="D39" s="54"/>
+      <c r="E39" s="55"/>
+      <c r="F39" s="55"/>
+      <c r="G39" s="55"/>
+      <c r="H39" s="55"/>
+      <c r="I39" s="55"/>
+      <c r="J39" s="55"/>
+      <c r="K39" s="55"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="55"/>
+      <c r="N39" s="55"/>
+      <c r="O39" s="55"/>
+      <c r="P39" s="55"/>
+      <c r="Q39" s="55"/>
+      <c r="R39" s="55"/>
+      <c r="S39" s="55"/>
+      <c r="T39" s="55"/>
+      <c r="U39" s="56"/>
     </row>
     <row r="40" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="49"/>
+      <c r="A40" s="46"/>
       <c r="B40" s="28" t="s">
         <v>83</v>
       </c>
       <c r="C40" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="D40" s="39"/>
-      <c r="E40" s="40"/>
-      <c r="F40" s="40"/>
-      <c r="G40" s="40"/>
-      <c r="H40" s="40"/>
-      <c r="I40" s="40"/>
-      <c r="J40" s="40"/>
-      <c r="K40" s="40"/>
-      <c r="L40" s="40"/>
-      <c r="M40" s="40"/>
-      <c r="N40" s="40"/>
-      <c r="O40" s="40"/>
-      <c r="P40" s="40"/>
-      <c r="Q40" s="40"/>
-      <c r="R40" s="40"/>
-      <c r="S40" s="40"/>
-      <c r="T40" s="40"/>
-      <c r="U40" s="41"/>
+      <c r="D40" s="54"/>
+      <c r="E40" s="55"/>
+      <c r="F40" s="55"/>
+      <c r="G40" s="55"/>
+      <c r="H40" s="55"/>
+      <c r="I40" s="55"/>
+      <c r="J40" s="55"/>
+      <c r="K40" s="55"/>
+      <c r="L40" s="55"/>
+      <c r="M40" s="55"/>
+      <c r="N40" s="55"/>
+      <c r="O40" s="55"/>
+      <c r="P40" s="55"/>
+      <c r="Q40" s="55"/>
+      <c r="R40" s="55"/>
+      <c r="S40" s="55"/>
+      <c r="T40" s="55"/>
+      <c r="U40" s="56"/>
     </row>
     <row r="41" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="49"/>
+      <c r="A41" s="46"/>
       <c r="B41" s="28" t="s">
         <v>84</v>
       </c>
       <c r="C41" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="D41" s="42"/>
-      <c r="E41" s="43"/>
-      <c r="F41" s="43"/>
-      <c r="G41" s="43"/>
-      <c r="H41" s="43"/>
-      <c r="I41" s="43"/>
-      <c r="J41" s="43"/>
-      <c r="K41" s="43"/>
-      <c r="L41" s="43"/>
-      <c r="M41" s="43"/>
-      <c r="N41" s="43"/>
-      <c r="O41" s="43"/>
-      <c r="P41" s="43"/>
-      <c r="Q41" s="43"/>
-      <c r="R41" s="43"/>
-      <c r="S41" s="43"/>
-      <c r="T41" s="43"/>
-      <c r="U41" s="44"/>
+      <c r="D41" s="57"/>
+      <c r="E41" s="58"/>
+      <c r="F41" s="58"/>
+      <c r="G41" s="58"/>
+      <c r="H41" s="58"/>
+      <c r="I41" s="58"/>
+      <c r="J41" s="58"/>
+      <c r="K41" s="58"/>
+      <c r="L41" s="58"/>
+      <c r="M41" s="58"/>
+      <c r="N41" s="58"/>
+      <c r="O41" s="58"/>
+      <c r="P41" s="58"/>
+      <c r="Q41" s="58"/>
+      <c r="R41" s="58"/>
+      <c r="S41" s="58"/>
+      <c r="T41" s="58"/>
+      <c r="U41" s="59"/>
     </row>
     <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="49"/>
+      <c r="A42" s="46"/>
       <c r="B42" s="29" t="s">
         <v>85</v>
       </c>
@@ -3120,7 +3117,7 @@
       <c r="U42" s="17"/>
     </row>
     <row r="43" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="49"/>
+      <c r="A43" s="46"/>
       <c r="B43" s="29" t="s">
         <v>86</v>
       </c>
@@ -3161,7 +3158,7 @@
       <c r="U43" s="17"/>
     </row>
     <row r="44" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="49"/>
+      <c r="A44" s="46"/>
       <c r="B44" s="30" t="s">
         <v>87</v>
       </c>
@@ -3188,7 +3185,7 @@
       <c r="U44" s="25"/>
     </row>
     <row r="45" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="50"/>
+      <c r="A45" s="47"/>
       <c r="B45" s="29" t="s">
         <v>88</v>
       </c>
@@ -3215,7 +3212,7 @@
       <c r="U45" s="17"/>
     </row>
     <row r="46" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="45">
+      <c r="A46" s="42">
         <v>7</v>
       </c>
       <c r="B46" s="11" t="s">
@@ -3243,7 +3240,7 @@
       <c r="U46" s="9"/>
     </row>
     <row r="47" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="46"/>
+      <c r="A47" s="43"/>
       <c r="B47" s="11" t="s">
         <v>90</v>
       </c>
@@ -3286,7 +3283,7 @@
       <c r="U47" s="9"/>
     </row>
     <row r="48" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="46"/>
+      <c r="A48" s="43"/>
       <c r="B48" s="11" t="s">
         <v>91</v>
       </c>
@@ -3329,7 +3326,7 @@
       <c r="U48" s="9"/>
     </row>
     <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A49" s="46"/>
+      <c r="A49" s="43"/>
       <c r="B49" s="11" t="s">
         <v>92</v>
       </c>
@@ -3372,7 +3369,7 @@
       <c r="U49" s="9"/>
     </row>
     <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A50" s="46"/>
+      <c r="A50" s="43"/>
       <c r="B50" s="11" t="s">
         <v>93</v>
       </c>
@@ -3413,7 +3410,7 @@
       <c r="U50" s="9"/>
     </row>
     <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A51" s="46"/>
+      <c r="A51" s="43"/>
       <c r="B51" s="11" t="s">
         <v>94</v>
       </c>
@@ -3448,7 +3445,7 @@
       <c r="U51" s="9"/>
     </row>
     <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="47"/>
+      <c r="A52" s="44"/>
       <c r="B52" s="11" t="s">
         <v>95</v>
       </c>
@@ -3475,7 +3472,7 @@
       <c r="U52" s="9"/>
     </row>
     <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="48">
+      <c r="A53" s="45">
         <v>8</v>
       </c>
       <c r="B53" s="29" t="s">
@@ -3508,7 +3505,7 @@
       <c r="U53" s="17"/>
     </row>
     <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="49"/>
+      <c r="A54" s="46"/>
       <c r="B54" s="29" t="s">
         <v>97</v>
       </c>
@@ -3539,7 +3536,7 @@
       <c r="U54" s="17"/>
     </row>
     <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="49"/>
+      <c r="A55" s="46"/>
       <c r="B55" s="29" t="s">
         <v>98</v>
       </c>
@@ -3582,7 +3579,7 @@
       </c>
     </row>
     <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="49"/>
+      <c r="A56" s="46"/>
       <c r="B56" s="29" t="s">
         <v>99</v>
       </c>
@@ -3625,7 +3622,7 @@
       <c r="U56" s="17"/>
     </row>
     <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="49"/>
+      <c r="A57" s="46"/>
       <c r="B57" s="29" t="s">
         <v>100</v>
       </c>
@@ -3668,7 +3665,7 @@
       <c r="U57" s="17"/>
     </row>
     <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="49"/>
+      <c r="A58" s="46"/>
       <c r="B58" s="29" t="s">
         <v>101</v>
       </c>
@@ -3703,7 +3700,7 @@
       <c r="U58" s="17"/>
     </row>
     <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="50"/>
+      <c r="A59" s="47"/>
       <c r="B59" s="29" t="s">
         <v>102</v>
       </c>
@@ -3730,7 +3727,7 @@
       <c r="U59" s="17"/>
     </row>
     <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="45">
+      <c r="A60" s="42">
         <v>9</v>
       </c>
       <c r="B60" s="11" t="s">
@@ -3758,7 +3755,7 @@
       <c r="U60" s="9"/>
     </row>
     <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="46"/>
+      <c r="A61" s="43"/>
       <c r="B61" s="11" t="s">
         <v>104</v>
       </c>
@@ -3789,7 +3786,7 @@
       <c r="U61" s="9"/>
     </row>
     <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="46"/>
+      <c r="A62" s="43"/>
       <c r="B62" s="11" t="s">
         <v>105</v>
       </c>
@@ -3832,7 +3829,7 @@
       </c>
     </row>
     <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="46"/>
+      <c r="A63" s="43"/>
       <c r="B63" s="11" t="s">
         <v>106</v>
       </c>
@@ -3875,7 +3872,7 @@
       <c r="U63" s="31"/>
     </row>
     <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="46"/>
+      <c r="A64" s="43"/>
       <c r="B64" s="11" t="s">
         <v>107</v>
       </c>
@@ -3889,7 +3886,7 @@
         <v>39</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="G64" s="6" t="s">
         <v>38</v>
@@ -3898,7 +3895,7 @@
         <v>39</v>
       </c>
       <c r="I64" s="9" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="J64" s="6" t="s">
         <v>17</v>
@@ -3918,9 +3915,9 @@
       <c r="U64" s="31"/>
     </row>
     <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="46"/>
+      <c r="A65" s="43"/>
       <c r="B65" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C65" s="7" t="s">
         <v>43</v>
@@ -3953,9 +3950,9 @@
       <c r="U65" s="31"/>
     </row>
     <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="47"/>
+      <c r="A66" s="44"/>
       <c r="B66" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C66" s="7" t="s">
         <v>47</v>
@@ -3980,11 +3977,11 @@
       <c r="U66" s="31"/>
     </row>
     <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="48">
+      <c r="A67" s="45">
         <v>10</v>
       </c>
       <c r="B67" s="29" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C67" s="15" t="s">
         <v>15</v>
@@ -4025,9 +4022,9 @@
       <c r="U67" s="32"/>
     </row>
     <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="49"/>
+      <c r="A68" s="46"/>
       <c r="B68" s="29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C68" s="15" t="s">
         <v>22</v>
@@ -4049,7 +4046,7 @@
         <v>50</v>
       </c>
       <c r="L68" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M68" s="14" t="s">
         <v>49</v>
@@ -4058,7 +4055,7 @@
         <v>50</v>
       </c>
       <c r="O68" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P68" s="14"/>
       <c r="Q68" s="16"/>
@@ -4068,9 +4065,9 @@
       <c r="U68" s="32"/>
     </row>
     <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="49"/>
+      <c r="A69" s="46"/>
       <c r="B69" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C69" s="15" t="s">
         <v>29</v>
@@ -4082,7 +4079,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G69" s="14" t="s">
         <v>49</v>
@@ -4091,7 +4088,7 @@
         <v>50</v>
       </c>
       <c r="I69" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J69" s="14" t="s">
         <v>16</v>
@@ -4111,9 +4108,9 @@
       <c r="U69" s="32"/>
     </row>
     <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="49"/>
+      <c r="A70" s="46"/>
       <c r="B70" s="29" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C70" s="15" t="s">
         <v>33</v>
@@ -4135,7 +4132,7 @@
         <v>50</v>
       </c>
       <c r="L70" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M70" s="14" t="s">
         <v>49</v>
@@ -4144,7 +4141,7 @@
         <v>50</v>
       </c>
       <c r="O70" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P70" s="14"/>
       <c r="Q70" s="16"/>
@@ -4154,9 +4151,9 @@
       <c r="U70" s="32"/>
     </row>
     <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="49"/>
+      <c r="A71" s="46"/>
       <c r="B71" s="29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C71" s="15" t="s">
         <v>37</v>
@@ -4168,7 +4165,7 @@
         <v>50</v>
       </c>
       <c r="F71" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G71" s="14" t="s">
         <v>49</v>
@@ -4177,7 +4174,7 @@
         <v>50</v>
       </c>
       <c r="I71" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J71" s="14" t="s">
         <v>17</v>
@@ -4197,9 +4194,9 @@
       <c r="U71" s="32"/>
     </row>
     <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A72" s="49"/>
+      <c r="A72" s="46"/>
       <c r="B72" s="29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C72" s="15" t="s">
         <v>43</v>
@@ -4211,7 +4208,7 @@
         <v>50</v>
       </c>
       <c r="F72" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G72" s="14" t="s">
         <v>49</v>
@@ -4220,7 +4217,7 @@
         <v>50</v>
       </c>
       <c r="I72" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J72" s="14" t="s">
         <v>49</v>
@@ -4229,7 +4226,7 @@
         <v>50</v>
       </c>
       <c r="L72" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M72" s="14" t="s">
         <v>49</v>
@@ -4238,7 +4235,7 @@
         <v>50</v>
       </c>
       <c r="O72" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P72" s="14"/>
       <c r="Q72" s="16"/>
@@ -4248,9 +4245,9 @@
       <c r="U72" s="32"/>
     </row>
     <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A73" s="50"/>
+      <c r="A73" s="47"/>
       <c r="B73" s="29" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C73" s="15" t="s">
         <v>47</v>
@@ -4275,11 +4272,11 @@
       <c r="U73" s="32"/>
     </row>
     <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A74" s="45">
+      <c r="A74" s="42">
         <v>11</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C74" s="7" t="s">
         <v>15</v>
@@ -4320,9 +4317,9 @@
       <c r="U74" s="31"/>
     </row>
     <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A75" s="46"/>
+      <c r="A75" s="43"/>
       <c r="B75" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C75" s="7" t="s">
         <v>22</v>
@@ -4344,7 +4341,7 @@
         <v>50</v>
       </c>
       <c r="L75" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M75" s="6" t="s">
         <v>49</v>
@@ -4353,7 +4350,7 @@
         <v>50</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P75" s="6"/>
       <c r="Q75" s="8"/>
@@ -4363,9 +4360,9 @@
       <c r="U75" s="31"/>
     </row>
     <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A76" s="46"/>
+      <c r="A76" s="43"/>
       <c r="B76" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C76" s="7" t="s">
         <v>29</v>
@@ -4377,7 +4374,7 @@
         <v>50</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G76" s="6" t="s">
         <v>49</v>
@@ -4386,7 +4383,7 @@
         <v>50</v>
       </c>
       <c r="I76" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J76" s="6" t="s">
         <v>16</v>
@@ -4418,9 +4415,9 @@
       </c>
     </row>
     <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A77" s="46"/>
+      <c r="A77" s="43"/>
       <c r="B77" s="11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C77" s="7" t="s">
         <v>33</v>
@@ -4442,7 +4439,7 @@
         <v>50</v>
       </c>
       <c r="L77" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M77" s="6" t="s">
         <v>49</v>
@@ -4451,7 +4448,7 @@
         <v>50</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P77" s="6"/>
       <c r="Q77" s="8"/>
@@ -4461,9 +4458,9 @@
       <c r="U77" s="9"/>
     </row>
     <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A78" s="46"/>
+      <c r="A78" s="43"/>
       <c r="B78" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C78" s="7" t="s">
         <v>37</v>
@@ -4475,7 +4472,7 @@
         <v>50</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G78" s="6" t="s">
         <v>49</v>
@@ -4484,7 +4481,7 @@
         <v>50</v>
       </c>
       <c r="I78" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J78" s="6" t="s">
         <v>17</v>
@@ -4504,9 +4501,9 @@
       <c r="U78" s="9"/>
     </row>
     <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A79" s="46"/>
+      <c r="A79" s="43"/>
       <c r="B79" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C79" s="7" t="s">
         <v>43</v>
@@ -4518,7 +4515,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G79" s="6" t="s">
         <v>49</v>
@@ -4527,7 +4524,7 @@
         <v>50</v>
       </c>
       <c r="I79" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J79" s="6" t="s">
         <v>49</v>
@@ -4536,7 +4533,7 @@
         <v>50</v>
       </c>
       <c r="L79" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M79" s="6" t="s">
         <v>49</v>
@@ -4545,7 +4542,7 @@
         <v>50</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P79" s="6"/>
       <c r="Q79" s="8"/>
@@ -4555,9 +4552,9 @@
       <c r="U79" s="9"/>
     </row>
     <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A80" s="47"/>
+      <c r="A80" s="44"/>
       <c r="B80" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C80" s="7" t="s">
         <v>47</v>
@@ -4582,11 +4579,11 @@
       <c r="U80" s="9"/>
     </row>
     <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A81" s="48">
+      <c r="A81" s="45">
         <v>12</v>
       </c>
       <c r="B81" s="29" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C81" s="15" t="s">
         <v>15</v>
@@ -4627,9 +4624,9 @@
       <c r="U81" s="17"/>
     </row>
     <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A82" s="49"/>
+      <c r="A82" s="46"/>
       <c r="B82" s="29" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C82" s="15" t="s">
         <v>22</v>
@@ -4648,19 +4645,19 @@
         <v>38</v>
       </c>
       <c r="K82" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="L82" s="17" t="s">
         <v>128</v>
-      </c>
-      <c r="L82" s="17" t="s">
-        <v>129</v>
       </c>
       <c r="M82" s="14" t="s">
         <v>38</v>
       </c>
       <c r="N82" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="O82" s="17" t="s">
         <v>128</v>
-      </c>
-      <c r="O82" s="17" t="s">
-        <v>129</v>
       </c>
       <c r="P82" s="14"/>
       <c r="Q82" s="16"/>
@@ -4670,9 +4667,9 @@
       <c r="U82" s="17"/>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="49"/>
+      <c r="A83" s="46"/>
       <c r="B83" s="29" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C83" s="15" t="s">
         <v>29</v>
@@ -4681,19 +4678,19 @@
         <v>45</v>
       </c>
       <c r="E83" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="F83" s="17" t="s">
         <v>128</v>
-      </c>
-      <c r="F83" s="17" t="s">
-        <v>129</v>
       </c>
       <c r="G83" s="14" t="s">
         <v>45</v>
       </c>
       <c r="H83" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="I83" s="17" t="s">
         <v>128</v>
-      </c>
-      <c r="I83" s="17" t="s">
-        <v>129</v>
       </c>
       <c r="J83" s="14" t="s">
         <v>16</v>
@@ -4706,28 +4703,28 @@
       <c r="N83" s="16"/>
       <c r="O83" s="17"/>
       <c r="P83" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q83" s="16" t="s">
         <v>131</v>
-      </c>
-      <c r="Q83" s="16" t="s">
-        <v>132</v>
       </c>
       <c r="R83" s="17" t="s">
         <v>55</v>
       </c>
       <c r="S83" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="T83" s="16" t="s">
         <v>131</v>
-      </c>
-      <c r="T83" s="16" t="s">
-        <v>132</v>
       </c>
       <c r="U83" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A84" s="49"/>
+      <c r="A84" s="46"/>
       <c r="B84" s="29" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C84" s="15" t="s">
         <v>33</v>
@@ -4746,19 +4743,19 @@
         <v>38</v>
       </c>
       <c r="K84" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="L84" s="17" t="s">
         <v>128</v>
-      </c>
-      <c r="L84" s="17" t="s">
-        <v>129</v>
       </c>
       <c r="M84" s="14" t="s">
         <v>38</v>
       </c>
       <c r="N84" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="O84" s="17" t="s">
         <v>128</v>
-      </c>
-      <c r="O84" s="17" t="s">
-        <v>129</v>
       </c>
       <c r="P84" s="14"/>
       <c r="Q84" s="16"/>
@@ -4768,9 +4765,9 @@
       <c r="U84" s="17"/>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="49"/>
+      <c r="A85" s="46"/>
       <c r="B85" s="29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C85" s="15" t="s">
         <v>37</v>
@@ -4779,19 +4776,19 @@
         <v>38</v>
       </c>
       <c r="E85" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="F85" s="17" t="s">
         <v>128</v>
-      </c>
-      <c r="F85" s="17" t="s">
-        <v>129</v>
       </c>
       <c r="G85" s="14" t="s">
         <v>38</v>
       </c>
       <c r="H85" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="I85" s="17" t="s">
         <v>128</v>
-      </c>
-      <c r="I85" s="17" t="s">
-        <v>129</v>
       </c>
       <c r="J85" s="14" t="s">
         <v>17</v>
@@ -4811,9 +4808,9 @@
       <c r="U85" s="17"/>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A86" s="49"/>
+      <c r="A86" s="46"/>
       <c r="B86" s="29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C86" s="15" t="s">
         <v>43</v>
@@ -4846,9 +4843,9 @@
       <c r="U86" s="17"/>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A87" s="50"/>
+      <c r="A87" s="47"/>
       <c r="B87" s="29" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C87" s="15" t="s">
         <v>47</v>
@@ -4873,11 +4870,11 @@
       <c r="U87" s="17"/>
     </row>
     <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A88" s="45">
+      <c r="A88" s="42">
         <v>13</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C88" s="7" t="s">
         <v>15</v>
@@ -4918,9 +4915,9 @@
       <c r="U88" s="9"/>
     </row>
     <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A89" s="46"/>
+      <c r="A89" s="43"/>
       <c r="B89" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C89" s="7" t="s">
         <v>22</v>
@@ -4939,19 +4936,19 @@
         <v>30</v>
       </c>
       <c r="K89" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="L89" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="L89" s="9" t="s">
-        <v>140</v>
       </c>
       <c r="M89" s="6" t="s">
         <v>30</v>
       </c>
       <c r="N89" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="O89" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="O89" s="9" t="s">
-        <v>140</v>
       </c>
       <c r="P89" s="6"/>
       <c r="Q89" s="8"/>
@@ -4961,9 +4958,9 @@
       <c r="U89" s="9"/>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A90" s="46"/>
+      <c r="A90" s="43"/>
       <c r="B90" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C90" s="7" t="s">
         <v>29</v>
@@ -4972,19 +4969,19 @@
         <v>30</v>
       </c>
       <c r="E90" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F90" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="F90" s="9" t="s">
-        <v>140</v>
       </c>
       <c r="G90" s="6" t="s">
         <v>30</v>
       </c>
       <c r="H90" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="I90" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="I90" s="9" t="s">
-        <v>140</v>
       </c>
       <c r="J90" s="6" t="s">
         <v>16</v>
@@ -4997,28 +4994,28 @@
       <c r="N90" s="8"/>
       <c r="O90" s="9"/>
       <c r="P90" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q90" s="8" t="s">
         <v>131</v>
-      </c>
-      <c r="Q90" s="8" t="s">
-        <v>132</v>
       </c>
       <c r="R90" s="9" t="s">
         <v>55</v>
       </c>
       <c r="S90" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="T90" s="8" t="s">
         <v>131</v>
-      </c>
-      <c r="T90" s="8" t="s">
-        <v>132</v>
       </c>
       <c r="U90" s="9" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A91" s="46"/>
+      <c r="A91" s="43"/>
       <c r="B91" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C91" s="7" t="s">
         <v>33</v>
@@ -5037,19 +5034,19 @@
         <v>30</v>
       </c>
       <c r="K91" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="L91" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="L91" s="9" t="s">
-        <v>140</v>
       </c>
       <c r="M91" s="6" t="s">
         <v>30</v>
       </c>
       <c r="N91" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="O91" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="O91" s="9" t="s">
-        <v>140</v>
       </c>
       <c r="P91" s="6"/>
       <c r="Q91" s="8"/>
@@ -5059,9 +5056,9 @@
       <c r="U91" s="9"/>
     </row>
     <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A92" s="46"/>
+      <c r="A92" s="43"/>
       <c r="B92" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C92" s="7" t="s">
         <v>37</v>
@@ -5070,19 +5067,19 @@
         <v>35</v>
       </c>
       <c r="E92" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F92" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="F92" s="9" t="s">
-        <v>140</v>
       </c>
       <c r="G92" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H92" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="I92" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="I92" s="9" t="s">
-        <v>140</v>
       </c>
       <c r="J92" s="6" t="s">
         <v>17</v>
@@ -5102,9 +5099,9 @@
       <c r="U92" s="9"/>
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A93" s="46"/>
+      <c r="A93" s="43"/>
       <c r="B93" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C93" s="7" t="s">
         <v>43</v>
@@ -5137,9 +5134,9 @@
       <c r="U93" s="9"/>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A94" s="47"/>
+      <c r="A94" s="44"/>
       <c r="B94" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C94" s="7" t="s">
         <v>47</v>
@@ -5164,11 +5161,11 @@
       <c r="U94" s="9"/>
     </row>
     <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A95" s="48">
+      <c r="A95" s="45">
         <v>14</v>
       </c>
       <c r="B95" s="29" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C95" s="15" t="s">
         <v>15</v>
@@ -5209,9 +5206,9 @@
       <c r="U95" s="17"/>
     </row>
     <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A96" s="49"/>
+      <c r="A96" s="46"/>
       <c r="B96" s="29" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C96" s="15" t="s">
         <v>22</v>
@@ -5230,19 +5227,19 @@
         <v>30</v>
       </c>
       <c r="K96" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="L96" s="17" t="s">
         <v>139</v>
-      </c>
-      <c r="L96" s="17" t="s">
-        <v>140</v>
       </c>
       <c r="M96" s="14" t="s">
         <v>30</v>
       </c>
       <c r="N96" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="O96" s="17" t="s">
         <v>139</v>
-      </c>
-      <c r="O96" s="17" t="s">
-        <v>140</v>
       </c>
       <c r="P96" s="14"/>
       <c r="Q96" s="16"/>
@@ -5252,9 +5249,9 @@
       <c r="U96" s="17"/>
     </row>
     <row r="97" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A97" s="49"/>
+      <c r="A97" s="46"/>
       <c r="B97" s="29" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C97" s="15" t="s">
         <v>29</v>
@@ -5263,19 +5260,19 @@
         <v>30</v>
       </c>
       <c r="E97" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="F97" s="17" t="s">
         <v>139</v>
-      </c>
-      <c r="F97" s="17" t="s">
-        <v>140</v>
       </c>
       <c r="G97" s="14" t="s">
         <v>30</v>
       </c>
       <c r="H97" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="I97" s="17" t="s">
         <v>139</v>
-      </c>
-      <c r="I97" s="17" t="s">
-        <v>140</v>
       </c>
       <c r="J97" s="14" t="s">
         <v>16</v>
@@ -5288,28 +5285,28 @@
       <c r="N97" s="16"/>
       <c r="O97" s="17"/>
       <c r="P97" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q97" s="16" t="s">
         <v>131</v>
-      </c>
-      <c r="Q97" s="16" t="s">
-        <v>132</v>
       </c>
       <c r="R97" s="17" t="s">
         <v>55</v>
       </c>
       <c r="S97" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="T97" s="16" t="s">
         <v>131</v>
-      </c>
-      <c r="T97" s="16" t="s">
-        <v>132</v>
       </c>
       <c r="U97" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="98" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A98" s="49"/>
+      <c r="A98" s="46"/>
       <c r="B98" s="29" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C98" s="15" t="s">
         <v>33</v>
@@ -5328,19 +5325,19 @@
         <v>30</v>
       </c>
       <c r="K98" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="L98" s="17" t="s">
         <v>139</v>
-      </c>
-      <c r="L98" s="17" t="s">
-        <v>140</v>
       </c>
       <c r="M98" s="14" t="s">
         <v>30</v>
       </c>
       <c r="N98" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="O98" s="17" t="s">
         <v>139</v>
-      </c>
-      <c r="O98" s="17" t="s">
-        <v>140</v>
       </c>
       <c r="P98" s="14"/>
       <c r="Q98" s="16"/>
@@ -5350,9 +5347,9 @@
       <c r="U98" s="17"/>
     </row>
     <row r="99" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A99" s="49"/>
+      <c r="A99" s="46"/>
       <c r="B99" s="29" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C99" s="15" t="s">
         <v>37</v>
@@ -5361,19 +5358,19 @@
         <v>35</v>
       </c>
       <c r="E99" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="F99" s="17" t="s">
         <v>139</v>
-      </c>
-      <c r="F99" s="17" t="s">
-        <v>140</v>
       </c>
       <c r="G99" s="14" t="s">
         <v>35</v>
       </c>
       <c r="H99" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="I99" s="17" t="s">
         <v>139</v>
-      </c>
-      <c r="I99" s="17" t="s">
-        <v>140</v>
       </c>
       <c r="J99" s="14" t="s">
         <v>17</v>
@@ -5393,9 +5390,9 @@
       <c r="U99" s="17"/>
     </row>
     <row r="100" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A100" s="49"/>
+      <c r="A100" s="46"/>
       <c r="B100" s="29" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C100" s="15" t="s">
         <v>43</v>
@@ -5420,9 +5417,9 @@
       <c r="U100" s="17"/>
     </row>
     <row r="101" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A101" s="50"/>
+      <c r="A101" s="47"/>
       <c r="B101" s="29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C101" s="15" t="s">
         <v>47</v>
@@ -5447,11 +5444,11 @@
       <c r="U101" s="17"/>
     </row>
     <row r="102" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="45">
+      <c r="A102" s="42">
         <v>15</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C102" s="7" t="s">
         <v>15</v>
@@ -5492,9 +5489,9 @@
       <c r="U102" s="9"/>
     </row>
     <row r="103" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A103" s="46"/>
+      <c r="A103" s="43"/>
       <c r="B103" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C103" s="7" t="s">
         <v>22</v>
@@ -5513,19 +5510,19 @@
         <v>30</v>
       </c>
       <c r="K103" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="L103" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="L103" s="9" t="s">
-        <v>140</v>
       </c>
       <c r="M103" s="6" t="s">
         <v>30</v>
       </c>
       <c r="N103" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="O103" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="O103" s="9" t="s">
-        <v>140</v>
       </c>
       <c r="P103" s="6"/>
       <c r="Q103" s="8"/>
@@ -5535,9 +5532,9 @@
       <c r="U103" s="9"/>
     </row>
     <row r="104" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="46"/>
+      <c r="A104" s="43"/>
       <c r="B104" s="11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C104" s="7" t="s">
         <v>29</v>
@@ -5546,19 +5543,19 @@
         <v>30</v>
       </c>
       <c r="E104" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F104" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="F104" s="9" t="s">
-        <v>140</v>
       </c>
       <c r="G104" s="6" t="s">
         <v>30</v>
       </c>
       <c r="H104" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="I104" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="I104" s="9" t="s">
-        <v>140</v>
       </c>
       <c r="J104" s="6" t="s">
         <v>16</v>
@@ -5571,28 +5568,28 @@
       <c r="N104" s="8"/>
       <c r="O104" s="9"/>
       <c r="P104" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q104" s="8" t="s">
         <v>131</v>
-      </c>
-      <c r="Q104" s="8" t="s">
-        <v>132</v>
       </c>
       <c r="R104" s="9" t="s">
         <v>55</v>
       </c>
       <c r="S104" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="T104" s="8" t="s">
         <v>131</v>
-      </c>
-      <c r="T104" s="8" t="s">
-        <v>132</v>
       </c>
       <c r="U104" s="9" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="105" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A105" s="46"/>
+      <c r="A105" s="43"/>
       <c r="B105" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C105" s="7" t="s">
         <v>33</v>
@@ -5611,19 +5608,19 @@
         <v>30</v>
       </c>
       <c r="K105" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="L105" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="L105" s="9" t="s">
-        <v>140</v>
       </c>
       <c r="M105" s="6" t="s">
         <v>30</v>
       </c>
       <c r="N105" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="O105" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="O105" s="9" t="s">
-        <v>140</v>
       </c>
       <c r="P105" s="6"/>
       <c r="Q105" s="8"/>
@@ -5633,9 +5630,9 @@
       <c r="U105" s="9"/>
     </row>
     <row r="106" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A106" s="46"/>
+      <c r="A106" s="43"/>
       <c r="B106" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C106" s="7" t="s">
         <v>37</v>
@@ -5644,19 +5641,19 @@
         <v>35</v>
       </c>
       <c r="E106" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F106" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="F106" s="9" t="s">
-        <v>140</v>
       </c>
       <c r="G106" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H106" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="I106" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="I106" s="9" t="s">
-        <v>140</v>
       </c>
       <c r="J106" s="6" t="s">
         <v>17</v>
@@ -5676,9 +5673,9 @@
       <c r="U106" s="9"/>
     </row>
     <row r="107" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A107" s="46"/>
+      <c r="A107" s="43"/>
       <c r="B107" s="11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C107" s="7" t="s">
         <v>43</v>
@@ -5711,9 +5708,9 @@
       <c r="U107" s="9"/>
     </row>
     <row r="108" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A108" s="47"/>
+      <c r="A108" s="44"/>
       <c r="B108" s="11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C108" s="7" t="s">
         <v>47</v>
@@ -5738,11 +5735,11 @@
       <c r="U108" s="9"/>
     </row>
     <row r="109" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A109" s="48">
+      <c r="A109" s="45">
         <v>16</v>
       </c>
       <c r="B109" s="29" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C109" s="15" t="s">
         <v>15</v>
@@ -5783,9 +5780,9 @@
       <c r="U109" s="32"/>
     </row>
     <row r="110" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A110" s="49"/>
+      <c r="A110" s="46"/>
       <c r="B110" s="29" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C110" s="15" t="s">
         <v>22</v>
@@ -5804,19 +5801,19 @@
         <v>38</v>
       </c>
       <c r="K110" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="L110" s="17" t="s">
         <v>128</v>
-      </c>
-      <c r="L110" s="17" t="s">
-        <v>129</v>
       </c>
       <c r="M110" s="14" t="s">
         <v>38</v>
       </c>
       <c r="N110" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="O110" s="17" t="s">
         <v>128</v>
-      </c>
-      <c r="O110" s="17" t="s">
-        <v>129</v>
       </c>
       <c r="P110" s="14"/>
       <c r="Q110" s="16"/>
@@ -5826,9 +5823,9 @@
       <c r="U110" s="32"/>
     </row>
     <row r="111" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A111" s="49"/>
+      <c r="A111" s="46"/>
       <c r="B111" s="29" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C111" s="15" t="s">
         <v>29</v>
@@ -5837,19 +5834,19 @@
         <v>45</v>
       </c>
       <c r="E111" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="F111" s="17" t="s">
         <v>128</v>
-      </c>
-      <c r="F111" s="17" t="s">
-        <v>129</v>
       </c>
       <c r="G111" s="14" t="s">
         <v>45</v>
       </c>
       <c r="H111" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="I111" s="17" t="s">
         <v>128</v>
-      </c>
-      <c r="I111" s="17" t="s">
-        <v>129</v>
       </c>
       <c r="J111" s="14" t="s">
         <v>16</v>
@@ -5862,28 +5859,28 @@
       <c r="N111" s="16"/>
       <c r="O111" s="17"/>
       <c r="P111" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q111" s="16" t="s">
         <v>131</v>
-      </c>
-      <c r="Q111" s="16" t="s">
-        <v>132</v>
       </c>
       <c r="R111" s="17" t="s">
         <v>55</v>
       </c>
       <c r="S111" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="T111" s="16" t="s">
         <v>131</v>
-      </c>
-      <c r="T111" s="16" t="s">
-        <v>132</v>
       </c>
       <c r="U111" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="112" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A112" s="49"/>
+      <c r="A112" s="46"/>
       <c r="B112" s="29" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C112" s="15" t="s">
         <v>33</v>
@@ -5902,19 +5899,19 @@
         <v>38</v>
       </c>
       <c r="K112" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="L112" s="17" t="s">
         <v>128</v>
-      </c>
-      <c r="L112" s="17" t="s">
-        <v>129</v>
       </c>
       <c r="M112" s="14" t="s">
         <v>38</v>
       </c>
       <c r="N112" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="O112" s="17" t="s">
         <v>128</v>
-      </c>
-      <c r="O112" s="17" t="s">
-        <v>129</v>
       </c>
       <c r="P112" s="14"/>
       <c r="Q112" s="16"/>
@@ -5924,9 +5921,9 @@
       <c r="U112" s="32"/>
     </row>
     <row r="113" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A113" s="49"/>
+      <c r="A113" s="46"/>
       <c r="B113" s="29" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C113" s="15" t="s">
         <v>37</v>
@@ -5935,19 +5932,19 @@
         <v>38</v>
       </c>
       <c r="E113" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="F113" s="17" t="s">
         <v>128</v>
-      </c>
-      <c r="F113" s="17" t="s">
-        <v>129</v>
       </c>
       <c r="G113" s="14" t="s">
         <v>38</v>
       </c>
       <c r="H113" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="I113" s="17" t="s">
         <v>128</v>
-      </c>
-      <c r="I113" s="17" t="s">
-        <v>129</v>
       </c>
       <c r="J113" s="14" t="s">
         <v>17</v>
@@ -5967,9 +5964,9 @@
       <c r="U113" s="32"/>
     </row>
     <row r="114" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A114" s="49"/>
+      <c r="A114" s="46"/>
       <c r="B114" s="29" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C114" s="15" t="s">
         <v>43</v>
@@ -5994,9 +5991,9 @@
       <c r="U114" s="32"/>
     </row>
     <row r="115" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A115" s="50"/>
+      <c r="A115" s="47"/>
       <c r="B115" s="29" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C115" s="15" t="s">
         <v>47</v>
@@ -6021,11 +6018,11 @@
       <c r="U115" s="32"/>
     </row>
     <row r="116" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A116" s="45">
+      <c r="A116" s="42">
         <v>17</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C116" s="7" t="s">
         <v>15</v>
@@ -6064,9 +6061,9 @@
       <c r="U116" s="9"/>
     </row>
     <row r="117" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A117" s="46"/>
+      <c r="A117" s="43"/>
       <c r="B117" s="11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C117" s="7" t="s">
         <v>22</v>
@@ -6083,19 +6080,19 @@
         <v>30</v>
       </c>
       <c r="K117" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="L117" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="L117" s="9" t="s">
-        <v>140</v>
       </c>
       <c r="M117" s="6" t="s">
         <v>30</v>
       </c>
       <c r="N117" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="O117" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="O117" s="9" t="s">
-        <v>140</v>
       </c>
       <c r="P117" s="6"/>
       <c r="Q117" s="8"/>
@@ -6105,9 +6102,9 @@
       <c r="U117" s="9"/>
     </row>
     <row r="118" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A118" s="46"/>
+      <c r="A118" s="43"/>
       <c r="B118" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C118" s="7" t="s">
         <v>29</v>
@@ -6116,19 +6113,19 @@
         <v>35</v>
       </c>
       <c r="E118" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F118" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="F118" s="9" t="s">
-        <v>140</v>
       </c>
       <c r="G118" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H118" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="I118" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="I118" s="9" t="s">
-        <v>140</v>
       </c>
       <c r="J118" s="6"/>
       <c r="K118" s="8"/>
@@ -6139,28 +6136,28 @@
       <c r="N118" s="8"/>
       <c r="O118" s="9"/>
       <c r="P118" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q118" s="8" t="s">
         <v>131</v>
-      </c>
-      <c r="Q118" s="8" t="s">
-        <v>132</v>
       </c>
       <c r="R118" s="9" t="s">
         <v>55</v>
       </c>
       <c r="S118" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="T118" s="8" t="s">
         <v>131</v>
-      </c>
-      <c r="T118" s="8" t="s">
-        <v>132</v>
       </c>
       <c r="U118" s="9" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="119" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A119" s="46"/>
+      <c r="A119" s="43"/>
       <c r="B119" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C119" s="7" t="s">
         <v>33</v>
@@ -6177,19 +6174,19 @@
         <v>30</v>
       </c>
       <c r="K119" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="L119" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="L119" s="9" t="s">
-        <v>140</v>
       </c>
       <c r="M119" s="6" t="s">
         <v>30</v>
       </c>
       <c r="N119" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="O119" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="O119" s="9" t="s">
-        <v>140</v>
       </c>
       <c r="P119" s="6"/>
       <c r="Q119" s="8"/>
@@ -6199,9 +6196,9 @@
       <c r="U119" s="9"/>
     </row>
     <row r="120" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A120" s="46"/>
+      <c r="A120" s="43"/>
       <c r="B120" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C120" s="7" t="s">
         <v>37</v>
@@ -6230,9 +6227,9 @@
       <c r="U120" s="9"/>
     </row>
     <row r="121" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="46"/>
+      <c r="A121" s="43"/>
       <c r="B121" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C121" s="7" t="s">
         <v>43</v>
@@ -6257,9 +6254,9 @@
       <c r="U121" s="9"/>
     </row>
     <row r="122" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A122" s="47"/>
+      <c r="A122" s="44"/>
       <c r="B122" s="11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C122" s="7" t="s">
         <v>47</v>
@@ -6284,388 +6281,388 @@
       <c r="U122" s="9"/>
     </row>
     <row r="123" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="48">
+      <c r="A123" s="45">
         <v>18</v>
       </c>
       <c r="B123" s="29" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C123" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D123" s="57" t="s">
+      <c r="D123" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="E123" s="34"/>
+      <c r="F123" s="34"/>
+      <c r="G123" s="34"/>
+      <c r="H123" s="34"/>
+      <c r="I123" s="34"/>
+      <c r="J123" s="34"/>
+      <c r="K123" s="34"/>
+      <c r="L123" s="34"/>
+      <c r="M123" s="34"/>
+      <c r="N123" s="34"/>
+      <c r="O123" s="34"/>
+      <c r="P123" s="34"/>
+      <c r="Q123" s="34"/>
+      <c r="R123" s="34"/>
+      <c r="S123" s="34"/>
+      <c r="T123" s="34"/>
+      <c r="U123" s="35"/>
+    </row>
+    <row r="124" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A124" s="46"/>
+      <c r="B124" s="29" t="s">
         <v>175</v>
-      </c>
-      <c r="E123" s="58"/>
-      <c r="F123" s="58"/>
-      <c r="G123" s="58"/>
-      <c r="H123" s="58"/>
-      <c r="I123" s="58"/>
-      <c r="J123" s="58"/>
-      <c r="K123" s="58"/>
-      <c r="L123" s="58"/>
-      <c r="M123" s="58"/>
-      <c r="N123" s="58"/>
-      <c r="O123" s="58"/>
-      <c r="P123" s="58"/>
-      <c r="Q123" s="58"/>
-      <c r="R123" s="58"/>
-      <c r="S123" s="58"/>
-      <c r="T123" s="58"/>
-      <c r="U123" s="59"/>
-    </row>
-    <row r="124" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="49"/>
-      <c r="B124" s="29" t="s">
-        <v>176</v>
       </c>
       <c r="C124" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D124" s="60"/>
-      <c r="E124" s="61"/>
-      <c r="F124" s="61"/>
-      <c r="G124" s="61"/>
-      <c r="H124" s="61"/>
-      <c r="I124" s="61"/>
-      <c r="J124" s="61"/>
-      <c r="K124" s="61"/>
-      <c r="L124" s="61"/>
-      <c r="M124" s="61"/>
-      <c r="N124" s="61"/>
-      <c r="O124" s="61"/>
-      <c r="P124" s="61"/>
-      <c r="Q124" s="61"/>
-      <c r="R124" s="61"/>
-      <c r="S124" s="61"/>
-      <c r="T124" s="61"/>
-      <c r="U124" s="62"/>
+      <c r="D124" s="36"/>
+      <c r="E124" s="37"/>
+      <c r="F124" s="37"/>
+      <c r="G124" s="37"/>
+      <c r="H124" s="37"/>
+      <c r="I124" s="37"/>
+      <c r="J124" s="37"/>
+      <c r="K124" s="37"/>
+      <c r="L124" s="37"/>
+      <c r="M124" s="37"/>
+      <c r="N124" s="37"/>
+      <c r="O124" s="37"/>
+      <c r="P124" s="37"/>
+      <c r="Q124" s="37"/>
+      <c r="R124" s="37"/>
+      <c r="S124" s="37"/>
+      <c r="T124" s="37"/>
+      <c r="U124" s="38"/>
     </row>
     <row r="125" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="49"/>
+      <c r="A125" s="46"/>
       <c r="B125" s="29" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C125" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D125" s="60"/>
-      <c r="E125" s="61"/>
-      <c r="F125" s="61"/>
-      <c r="G125" s="61"/>
-      <c r="H125" s="61"/>
-      <c r="I125" s="61"/>
-      <c r="J125" s="61"/>
-      <c r="K125" s="61"/>
-      <c r="L125" s="61"/>
-      <c r="M125" s="61"/>
-      <c r="N125" s="61"/>
-      <c r="O125" s="61"/>
-      <c r="P125" s="61"/>
-      <c r="Q125" s="61"/>
-      <c r="R125" s="61"/>
-      <c r="S125" s="61"/>
-      <c r="T125" s="61"/>
-      <c r="U125" s="62"/>
+      <c r="D125" s="36"/>
+      <c r="E125" s="37"/>
+      <c r="F125" s="37"/>
+      <c r="G125" s="37"/>
+      <c r="H125" s="37"/>
+      <c r="I125" s="37"/>
+      <c r="J125" s="37"/>
+      <c r="K125" s="37"/>
+      <c r="L125" s="37"/>
+      <c r="M125" s="37"/>
+      <c r="N125" s="37"/>
+      <c r="O125" s="37"/>
+      <c r="P125" s="37"/>
+      <c r="Q125" s="37"/>
+      <c r="R125" s="37"/>
+      <c r="S125" s="37"/>
+      <c r="T125" s="37"/>
+      <c r="U125" s="38"/>
     </row>
     <row r="126" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A126" s="49"/>
+      <c r="A126" s="46"/>
       <c r="B126" s="29" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C126" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D126" s="60"/>
-      <c r="E126" s="61"/>
-      <c r="F126" s="61"/>
-      <c r="G126" s="61"/>
-      <c r="H126" s="61"/>
-      <c r="I126" s="61"/>
-      <c r="J126" s="61"/>
-      <c r="K126" s="61"/>
-      <c r="L126" s="61"/>
-      <c r="M126" s="61"/>
-      <c r="N126" s="61"/>
-      <c r="O126" s="61"/>
-      <c r="P126" s="61"/>
-      <c r="Q126" s="61"/>
-      <c r="R126" s="61"/>
-      <c r="S126" s="61"/>
-      <c r="T126" s="61"/>
-      <c r="U126" s="62"/>
+      <c r="D126" s="36"/>
+      <c r="E126" s="37"/>
+      <c r="F126" s="37"/>
+      <c r="G126" s="37"/>
+      <c r="H126" s="37"/>
+      <c r="I126" s="37"/>
+      <c r="J126" s="37"/>
+      <c r="K126" s="37"/>
+      <c r="L126" s="37"/>
+      <c r="M126" s="37"/>
+      <c r="N126" s="37"/>
+      <c r="O126" s="37"/>
+      <c r="P126" s="37"/>
+      <c r="Q126" s="37"/>
+      <c r="R126" s="37"/>
+      <c r="S126" s="37"/>
+      <c r="T126" s="37"/>
+      <c r="U126" s="38"/>
     </row>
     <row r="127" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A127" s="49"/>
+      <c r="A127" s="46"/>
       <c r="B127" s="28" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C127" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="D127" s="60"/>
-      <c r="E127" s="61"/>
-      <c r="F127" s="61"/>
-      <c r="G127" s="61"/>
-      <c r="H127" s="61"/>
-      <c r="I127" s="61"/>
-      <c r="J127" s="61"/>
-      <c r="K127" s="61"/>
-      <c r="L127" s="61"/>
-      <c r="M127" s="61"/>
-      <c r="N127" s="61"/>
-      <c r="O127" s="61"/>
-      <c r="P127" s="61"/>
-      <c r="Q127" s="61"/>
-      <c r="R127" s="61"/>
-      <c r="S127" s="61"/>
-      <c r="T127" s="61"/>
-      <c r="U127" s="62"/>
+      <c r="D127" s="36"/>
+      <c r="E127" s="37"/>
+      <c r="F127" s="37"/>
+      <c r="G127" s="37"/>
+      <c r="H127" s="37"/>
+      <c r="I127" s="37"/>
+      <c r="J127" s="37"/>
+      <c r="K127" s="37"/>
+      <c r="L127" s="37"/>
+      <c r="M127" s="37"/>
+      <c r="N127" s="37"/>
+      <c r="O127" s="37"/>
+      <c r="P127" s="37"/>
+      <c r="Q127" s="37"/>
+      <c r="R127" s="37"/>
+      <c r="S127" s="37"/>
+      <c r="T127" s="37"/>
+      <c r="U127" s="38"/>
     </row>
     <row r="128" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="49"/>
+      <c r="A128" s="46"/>
       <c r="B128" s="29" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C128" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D128" s="60"/>
-      <c r="E128" s="61"/>
-      <c r="F128" s="61"/>
-      <c r="G128" s="61"/>
-      <c r="H128" s="61"/>
-      <c r="I128" s="61"/>
-      <c r="J128" s="61"/>
-      <c r="K128" s="61"/>
-      <c r="L128" s="61"/>
-      <c r="M128" s="61"/>
-      <c r="N128" s="61"/>
-      <c r="O128" s="61"/>
-      <c r="P128" s="61"/>
-      <c r="Q128" s="61"/>
-      <c r="R128" s="61"/>
-      <c r="S128" s="61"/>
-      <c r="T128" s="61"/>
-      <c r="U128" s="62"/>
+      <c r="D128" s="36"/>
+      <c r="E128" s="37"/>
+      <c r="F128" s="37"/>
+      <c r="G128" s="37"/>
+      <c r="H128" s="37"/>
+      <c r="I128" s="37"/>
+      <c r="J128" s="37"/>
+      <c r="K128" s="37"/>
+      <c r="L128" s="37"/>
+      <c r="M128" s="37"/>
+      <c r="N128" s="37"/>
+      <c r="O128" s="37"/>
+      <c r="P128" s="37"/>
+      <c r="Q128" s="37"/>
+      <c r="R128" s="37"/>
+      <c r="S128" s="37"/>
+      <c r="T128" s="37"/>
+      <c r="U128" s="38"/>
     </row>
     <row r="129" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A129" s="50"/>
+      <c r="A129" s="47"/>
       <c r="B129" s="29" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C129" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D129" s="60"/>
-      <c r="E129" s="61"/>
-      <c r="F129" s="61"/>
-      <c r="G129" s="61"/>
-      <c r="H129" s="61"/>
-      <c r="I129" s="61"/>
-      <c r="J129" s="61"/>
-      <c r="K129" s="61"/>
-      <c r="L129" s="61"/>
-      <c r="M129" s="61"/>
-      <c r="N129" s="61"/>
-      <c r="O129" s="61"/>
-      <c r="P129" s="61"/>
-      <c r="Q129" s="61"/>
-      <c r="R129" s="61"/>
-      <c r="S129" s="61"/>
-      <c r="T129" s="61"/>
-      <c r="U129" s="62"/>
+      <c r="D129" s="36"/>
+      <c r="E129" s="37"/>
+      <c r="F129" s="37"/>
+      <c r="G129" s="37"/>
+      <c r="H129" s="37"/>
+      <c r="I129" s="37"/>
+      <c r="J129" s="37"/>
+      <c r="K129" s="37"/>
+      <c r="L129" s="37"/>
+      <c r="M129" s="37"/>
+      <c r="N129" s="37"/>
+      <c r="O129" s="37"/>
+      <c r="P129" s="37"/>
+      <c r="Q129" s="37"/>
+      <c r="R129" s="37"/>
+      <c r="S129" s="37"/>
+      <c r="T129" s="37"/>
+      <c r="U129" s="38"/>
     </row>
     <row r="130" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A130" s="45">
+      <c r="A130" s="42">
         <v>19</v>
       </c>
       <c r="B130" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C130" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D130" s="60"/>
-      <c r="E130" s="61"/>
-      <c r="F130" s="61"/>
-      <c r="G130" s="61"/>
-      <c r="H130" s="61"/>
-      <c r="I130" s="61"/>
-      <c r="J130" s="61"/>
-      <c r="K130" s="61"/>
-      <c r="L130" s="61"/>
-      <c r="M130" s="61"/>
-      <c r="N130" s="61"/>
-      <c r="O130" s="61"/>
-      <c r="P130" s="61"/>
-      <c r="Q130" s="61"/>
-      <c r="R130" s="61"/>
-      <c r="S130" s="61"/>
-      <c r="T130" s="61"/>
-      <c r="U130" s="62"/>
+      <c r="D130" s="36"/>
+      <c r="E130" s="37"/>
+      <c r="F130" s="37"/>
+      <c r="G130" s="37"/>
+      <c r="H130" s="37"/>
+      <c r="I130" s="37"/>
+      <c r="J130" s="37"/>
+      <c r="K130" s="37"/>
+      <c r="L130" s="37"/>
+      <c r="M130" s="37"/>
+      <c r="N130" s="37"/>
+      <c r="O130" s="37"/>
+      <c r="P130" s="37"/>
+      <c r="Q130" s="37"/>
+      <c r="R130" s="37"/>
+      <c r="S130" s="37"/>
+      <c r="T130" s="37"/>
+      <c r="U130" s="38"/>
     </row>
     <row r="131" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A131" s="46"/>
+      <c r="A131" s="43"/>
       <c r="B131" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C131" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D131" s="60"/>
-      <c r="E131" s="61"/>
-      <c r="F131" s="61"/>
-      <c r="G131" s="61"/>
-      <c r="H131" s="61"/>
-      <c r="I131" s="61"/>
-      <c r="J131" s="61"/>
-      <c r="K131" s="61"/>
-      <c r="L131" s="61"/>
-      <c r="M131" s="61"/>
-      <c r="N131" s="61"/>
-      <c r="O131" s="61"/>
-      <c r="P131" s="61"/>
-      <c r="Q131" s="61"/>
-      <c r="R131" s="61"/>
-      <c r="S131" s="61"/>
-      <c r="T131" s="61"/>
-      <c r="U131" s="62"/>
+      <c r="D131" s="36"/>
+      <c r="E131" s="37"/>
+      <c r="F131" s="37"/>
+      <c r="G131" s="37"/>
+      <c r="H131" s="37"/>
+      <c r="I131" s="37"/>
+      <c r="J131" s="37"/>
+      <c r="K131" s="37"/>
+      <c r="L131" s="37"/>
+      <c r="M131" s="37"/>
+      <c r="N131" s="37"/>
+      <c r="O131" s="37"/>
+      <c r="P131" s="37"/>
+      <c r="Q131" s="37"/>
+      <c r="R131" s="37"/>
+      <c r="S131" s="37"/>
+      <c r="T131" s="37"/>
+      <c r="U131" s="38"/>
     </row>
     <row r="132" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A132" s="46"/>
+      <c r="A132" s="43"/>
       <c r="B132" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C132" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D132" s="60"/>
-      <c r="E132" s="61"/>
-      <c r="F132" s="61"/>
-      <c r="G132" s="61"/>
-      <c r="H132" s="61"/>
-      <c r="I132" s="61"/>
-      <c r="J132" s="61"/>
-      <c r="K132" s="61"/>
-      <c r="L132" s="61"/>
-      <c r="M132" s="61"/>
-      <c r="N132" s="61"/>
-      <c r="O132" s="61"/>
-      <c r="P132" s="61"/>
-      <c r="Q132" s="61"/>
-      <c r="R132" s="61"/>
-      <c r="S132" s="61"/>
-      <c r="T132" s="61"/>
-      <c r="U132" s="62"/>
+      <c r="D132" s="36"/>
+      <c r="E132" s="37"/>
+      <c r="F132" s="37"/>
+      <c r="G132" s="37"/>
+      <c r="H132" s="37"/>
+      <c r="I132" s="37"/>
+      <c r="J132" s="37"/>
+      <c r="K132" s="37"/>
+      <c r="L132" s="37"/>
+      <c r="M132" s="37"/>
+      <c r="N132" s="37"/>
+      <c r="O132" s="37"/>
+      <c r="P132" s="37"/>
+      <c r="Q132" s="37"/>
+      <c r="R132" s="37"/>
+      <c r="S132" s="37"/>
+      <c r="T132" s="37"/>
+      <c r="U132" s="38"/>
     </row>
     <row r="133" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A133" s="46"/>
+      <c r="A133" s="43"/>
       <c r="B133" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C133" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D133" s="60"/>
-      <c r="E133" s="61"/>
-      <c r="F133" s="61"/>
-      <c r="G133" s="61"/>
-      <c r="H133" s="61"/>
-      <c r="I133" s="61"/>
-      <c r="J133" s="61"/>
-      <c r="K133" s="61"/>
-      <c r="L133" s="61"/>
-      <c r="M133" s="61"/>
-      <c r="N133" s="61"/>
-      <c r="O133" s="61"/>
-      <c r="P133" s="61"/>
-      <c r="Q133" s="61"/>
-      <c r="R133" s="61"/>
-      <c r="S133" s="61"/>
-      <c r="T133" s="61"/>
-      <c r="U133" s="62"/>
+      <c r="D133" s="36"/>
+      <c r="E133" s="37"/>
+      <c r="F133" s="37"/>
+      <c r="G133" s="37"/>
+      <c r="H133" s="37"/>
+      <c r="I133" s="37"/>
+      <c r="J133" s="37"/>
+      <c r="K133" s="37"/>
+      <c r="L133" s="37"/>
+      <c r="M133" s="37"/>
+      <c r="N133" s="37"/>
+      <c r="O133" s="37"/>
+      <c r="P133" s="37"/>
+      <c r="Q133" s="37"/>
+      <c r="R133" s="37"/>
+      <c r="S133" s="37"/>
+      <c r="T133" s="37"/>
+      <c r="U133" s="38"/>
     </row>
     <row r="134" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A134" s="46"/>
+      <c r="A134" s="43"/>
       <c r="B134" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C134" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D134" s="60"/>
-      <c r="E134" s="61"/>
-      <c r="F134" s="61"/>
-      <c r="G134" s="61"/>
-      <c r="H134" s="61"/>
-      <c r="I134" s="61"/>
-      <c r="J134" s="61"/>
-      <c r="K134" s="61"/>
-      <c r="L134" s="61"/>
-      <c r="M134" s="61"/>
-      <c r="N134" s="61"/>
-      <c r="O134" s="61"/>
-      <c r="P134" s="61"/>
-      <c r="Q134" s="61"/>
-      <c r="R134" s="61"/>
-      <c r="S134" s="61"/>
-      <c r="T134" s="61"/>
-      <c r="U134" s="62"/>
+      <c r="D134" s="36"/>
+      <c r="E134" s="37"/>
+      <c r="F134" s="37"/>
+      <c r="G134" s="37"/>
+      <c r="H134" s="37"/>
+      <c r="I134" s="37"/>
+      <c r="J134" s="37"/>
+      <c r="K134" s="37"/>
+      <c r="L134" s="37"/>
+      <c r="M134" s="37"/>
+      <c r="N134" s="37"/>
+      <c r="O134" s="37"/>
+      <c r="P134" s="37"/>
+      <c r="Q134" s="37"/>
+      <c r="R134" s="37"/>
+      <c r="S134" s="37"/>
+      <c r="T134" s="37"/>
+      <c r="U134" s="38"/>
     </row>
     <row r="135" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A135" s="46"/>
+      <c r="A135" s="43"/>
       <c r="B135" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C135" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D135" s="60"/>
-      <c r="E135" s="61"/>
-      <c r="F135" s="61"/>
-      <c r="G135" s="61"/>
-      <c r="H135" s="61"/>
-      <c r="I135" s="61"/>
-      <c r="J135" s="61"/>
-      <c r="K135" s="61"/>
-      <c r="L135" s="61"/>
-      <c r="M135" s="61"/>
-      <c r="N135" s="61"/>
-      <c r="O135" s="61"/>
-      <c r="P135" s="61"/>
-      <c r="Q135" s="61"/>
-      <c r="R135" s="61"/>
-      <c r="S135" s="61"/>
-      <c r="T135" s="61"/>
-      <c r="U135" s="62"/>
+      <c r="D135" s="36"/>
+      <c r="E135" s="37"/>
+      <c r="F135" s="37"/>
+      <c r="G135" s="37"/>
+      <c r="H135" s="37"/>
+      <c r="I135" s="37"/>
+      <c r="J135" s="37"/>
+      <c r="K135" s="37"/>
+      <c r="L135" s="37"/>
+      <c r="M135" s="37"/>
+      <c r="N135" s="37"/>
+      <c r="O135" s="37"/>
+      <c r="P135" s="37"/>
+      <c r="Q135" s="37"/>
+      <c r="R135" s="37"/>
+      <c r="S135" s="37"/>
+      <c r="T135" s="37"/>
+      <c r="U135" s="38"/>
     </row>
     <row r="136" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A136" s="47"/>
+      <c r="A136" s="44"/>
       <c r="B136" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C136" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D136" s="63"/>
-      <c r="E136" s="64"/>
-      <c r="F136" s="64"/>
-      <c r="G136" s="64"/>
-      <c r="H136" s="64"/>
-      <c r="I136" s="64"/>
-      <c r="J136" s="64"/>
-      <c r="K136" s="64"/>
-      <c r="L136" s="64"/>
-      <c r="M136" s="64"/>
-      <c r="N136" s="64"/>
-      <c r="O136" s="64"/>
-      <c r="P136" s="64"/>
-      <c r="Q136" s="64"/>
-      <c r="R136" s="64"/>
-      <c r="S136" s="64"/>
-      <c r="T136" s="64"/>
-      <c r="U136" s="65"/>
+      <c r="D136" s="39"/>
+      <c r="E136" s="40"/>
+      <c r="F136" s="40"/>
+      <c r="G136" s="40"/>
+      <c r="H136" s="40"/>
+      <c r="I136" s="40"/>
+      <c r="J136" s="40"/>
+      <c r="K136" s="40"/>
+      <c r="L136" s="40"/>
+      <c r="M136" s="40"/>
+      <c r="N136" s="40"/>
+      <c r="O136" s="40"/>
+      <c r="P136" s="40"/>
+      <c r="Q136" s="40"/>
+      <c r="R136" s="40"/>
+      <c r="S136" s="40"/>
+      <c r="T136" s="40"/>
+      <c r="U136" s="41"/>
     </row>
     <row r="137" spans="1:21"/>
     <row r="138" spans="1:21"/>
@@ -6683,26 +6680,6 @@
     <row r="150"/>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="D123:U136"/>
-    <mergeCell ref="A130:A136"/>
-    <mergeCell ref="A88:A94"/>
-    <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A102:A108"/>
-    <mergeCell ref="A109:A115"/>
-    <mergeCell ref="A116:A122"/>
-    <mergeCell ref="A123:A129"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="A81:A87"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A17"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="A25:A31"/>
-    <mergeCell ref="A46:A52"/>
-    <mergeCell ref="A53:A59"/>
-    <mergeCell ref="A60:A66"/>
-    <mergeCell ref="A67:A73"/>
-    <mergeCell ref="A74:A80"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="D29:U31"/>
@@ -6719,6 +6696,26 @@
     <mergeCell ref="S3:U3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:C3"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="A81:A87"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="A46:A52"/>
+    <mergeCell ref="A53:A59"/>
+    <mergeCell ref="A60:A66"/>
+    <mergeCell ref="A67:A73"/>
+    <mergeCell ref="A74:A80"/>
+    <mergeCell ref="D123:U136"/>
+    <mergeCell ref="A130:A136"/>
+    <mergeCell ref="A88:A94"/>
+    <mergeCell ref="A95:A101"/>
+    <mergeCell ref="A102:A108"/>
+    <mergeCell ref="A109:A115"/>
+    <mergeCell ref="A116:A122"/>
+    <mergeCell ref="A123:A129"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
